--- a/ĆWICZENIA.xlsx
+++ b/ĆWICZENIA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DYSK GOOGLE\ĆWICZENIA KONSPEKT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9EF689A-63EE-4DC0-A63A-752EAD841F58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B59FEF0-FBE9-48DE-B5FB-BD96A57CAE59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ćwiczenia" sheetId="1" r:id="rId1"/>
@@ -748,10 +748,10 @@
     <hyperlink ref="E3" r:id="rId2" xr:uid="{B41FAB88-E51F-43D8-B057-ACD206F129FB}"/>
     <hyperlink ref="E4" r:id="rId3" xr:uid="{14B9C1B5-749C-4628-A58D-91E70CDE055B}"/>
     <hyperlink ref="E5" r:id="rId4" xr:uid="{7B793A24-6321-4979-B5CA-05E4D6AC508F}"/>
-    <hyperlink ref="F2" r:id="rId5" xr:uid="{313F7E2C-B0E2-495B-8F1E-F61819672948}"/>
-    <hyperlink ref="F3" r:id="rId6" xr:uid="{AE23D867-EE88-4AE7-9665-53A44D1DF40E}"/>
-    <hyperlink ref="F5" r:id="rId7" xr:uid="{4742F3BF-7B21-4DC6-A19D-2D19100B5BBE}"/>
-    <hyperlink ref="F4" r:id="rId8" xr:uid="{76CA7736-17B4-4E43-8D26-528439AEAB53}"/>
+    <hyperlink ref="F2" r:id="rId5" xr:uid="{23132CF4-8A0D-40A4-843B-5F60F4DF4864}"/>
+    <hyperlink ref="F3" r:id="rId6" xr:uid="{D8320BEE-2538-429C-A448-28FADAFFB720}"/>
+    <hyperlink ref="F4" r:id="rId7" xr:uid="{9E805AD2-400A-4DEE-A2EC-7F39F4D305A1}"/>
+    <hyperlink ref="F5" r:id="rId8" xr:uid="{D0F8C780-CFAE-4C3F-B39E-8233AAA41BA7}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ĆWICZENIA.xlsx
+++ b/ĆWICZENIA.xlsx
@@ -8,16 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DYSK GOOGLE\ĆWICZENIA KONSPEKT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F01FE71-F81C-4379-82AD-4B7B4662E138}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9555A37F-7E1E-4D51-B647-088DA76AAF89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13305" yWindow="0" windowWidth="25200" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ćwiczenia" sheetId="1" r:id="rId1"/>
     <sheet name="INSTRUKCJA" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -26,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="80">
   <si>
     <t>NAZWA</t>
   </si>
@@ -52,36 +63,9 @@
     <t>Średni</t>
   </si>
   <si>
-    <t>szybkość, płynność, lewa ręka</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/</t>
-  </si>
-  <si>
     <t>Zaawansowany</t>
   </si>
   <si>
-    <t>szybkość, synchronizacja, kostka</t>
-  </si>
-  <si>
-    <t>siła, barre, akordy</t>
-  </si>
-  <si>
-    <t>synchronizacja, precyzja, rytm</t>
-  </si>
-  <si>
-    <t>Shred na gamie durowej</t>
-  </si>
-  <si>
-    <t>Shred</t>
-  </si>
-  <si>
-    <t>szybkość, shred, gamy</t>
-  </si>
-  <si>
-    <t>Rozgrzewka shredowa na gamie durowej w pozycji V.</t>
-  </si>
-  <si>
     <t>W SZPONACH GITARY — INSTRUKCJA ARKUSZA</t>
   </si>
   <si>
@@ -169,16 +153,130 @@
     <t>Krótka etiuda ogrywająca akordy w ciekawy sposób.</t>
   </si>
   <si>
-    <t>https://drive.google.com/uc?export=view&amp;id=1emXUmJs70wS68hiq71bHrOGz0TUur4Gh</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/uc?export=view&amp;id=13Tnhbuvbr9lMHz0-UYtuZpa5KuMeiXA-</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/uc?export=view&amp;id=1aEnjg_0osW5eYm01nzSiAuPwdZFB3xuS</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/uc?export=view&amp;id=1xezm-2cxHGI2nSFzCnX4QP3uI-bE5rXT</t>
+    <t>ECONOMY PICKING - Simple Arpegios</t>
+  </si>
+  <si>
+    <t>ECONOMY PICKING</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1jYGPekSJhVP65-xF8hpMjvbZ2Xgfl2I1&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1U1qi5R1KBhpjYVsMPXtxPhqrpg77iita&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>FINGERSTYLE</t>
+  </si>
+  <si>
+    <t>FINGERSTYLE - Boom Chick</t>
+  </si>
+  <si>
+    <t>FINGERSTYLE - Ćwiczenie na akordy ze slapem</t>
+  </si>
+  <si>
+    <t>FINGERSTYLE - Ćwiczenie na wybrzmiewanie i niezależność</t>
+  </si>
+  <si>
+    <t>FINGERSTYLE - Etiuda Promienne Slapy</t>
+  </si>
+  <si>
+    <t>FINGERSTYLE - Przebieg po skali E dur z pustą struną E6</t>
+  </si>
+  <si>
+    <t>FINGERSTYLE - Schemat ogrywania akordów - T12</t>
+  </si>
+  <si>
+    <t>FINGERSTYLE - Wesoła Etiuda C dur</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1xp9lIJR9VV69EG7aVRRlJYXOCsajvJuI&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=111s0l7r6sCiOJcQWzr5YhNmN64a_2_6G&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1ziJnH3GgDQdeczELoGxjRpOHPtMR_R7W&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=124dT8MB7tBsji-sBgen8-r7m_yM6wvT_&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1zwSOed6vzx77tWvGaDhteeEBLBregJNH&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1zHG9JTzf77pvAdnNWHq9KL8Cc4UzqfgH&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1y3Nc-rESbJydt8z5HnBScEY35zd8f64V&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Picking, Economy Picking, Arpeggio, Synchronizacja, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Krótka etiuda wykorzystująca ekonomię Picking w dół, dzięki której nauczysz się ogrywać arpeggia w ciekawy sposób. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ćwiczenie na obustronny ekonomii picking. Dwie struny po całej długości gryfu. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ćwiczenie na ogrywanie akordów pazurkiem w stylu Thomiego Emanuela i Cheta Atkinsa. </t>
+  </si>
+  <si>
+    <t>Prosty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ćwiczenie na slapy perkusyjne oraz ogrywanie akordów. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ćwiczenie na ogrywanie akordów z dodatkiem melodii. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Utwór, który napisałem dla córki, który równie dobrze sprawdza się jako etiuda fingerstyle'a. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fingerstyle, Etiuda, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECONOMY PICKING - Two Strings, Two Directions, Shred, </t>
+  </si>
+  <si>
+    <t>Pick Slanting, Shred, Picking, Synchronizacja, Lewa Ręka</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Szybkość, Płynność, Lewa Ręka, </t>
+  </si>
+  <si>
+    <t>Synchronizacja, Precyzja, Rytm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Picking, Szybkość, Synchronizacja, Arpeggio, Akordy, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fingerstyle, Prawa Ręka, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fingerstyle, Skale, Lewa Ręka, Prawa Ręka, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fingerstyle, Akordy, Slap, Lewa Ręka, Prawa Ręka, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fingerstyle, Niezależność palców, Prawa Ręka, Prawa Ręka, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fingerstyle, Slap, Prawa Ręka, Lewa Ręka, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fingerstyle, Akordy, Lewa Ręka, Prawa Ręka, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ćwiczenie na ogrywanie skali E-dur wraz z pompującym basem na strunie E6. </t>
+  </si>
+  <si>
+    <t>Ćwiczenie na ogrywanie akordów. Wedle schematu prawej ręki: Kciuk, Wskazujący, Środkowy palec</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ćwiczenie na niezależne granie melodii oraz basu jednocześnie w rytmie lekkiego shuffle. </t>
   </si>
 </sst>
 </file>
@@ -595,14 +693,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="40" customWidth="1"/>
-    <col min="5" max="6" width="50" customWidth="1"/>
+    <col min="5" max="5" width="50" customWidth="1"/>
+    <col min="6" max="6" width="2.42578125" customWidth="1"/>
     <col min="7" max="7" width="60" customWidth="1"/>
   </cols>
   <sheetData>
@@ -629,118 +728,375 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D2" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2" s="6"/>
+      <c r="G2" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="D3" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F3" s="7"/>
+      <c r="G3" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="F4" s="6"/>
+      <c r="G4" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="F2" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>13</v>
+        <v>69</v>
       </c>
       <c r="E5" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="F5" s="7"/>
+      <c r="G5" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="C6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="F6" s="6"/>
+      <c r="G6" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="F7" s="7"/>
+      <c r="G7" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E8" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="F8" s="6"/>
+      <c r="G8" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="F9" s="7"/>
+      <c r="G9" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="F10" s="6"/>
+      <c r="G10" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2" t="s">
-        <v>17</v>
-      </c>
+      <c r="B11" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="F11" s="7"/>
+      <c r="G11" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F12" s="6"/>
+      <c r="G12" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="F13" s="7"/>
+      <c r="G13" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="F14" s="6"/>
+      <c r="G14" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="3"/>
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="3"/>
+    </row>
+    <row r="16" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="2"/>
+    </row>
+    <row r="17" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="3"/>
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="3"/>
+    </row>
+    <row r="18" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="2"/>
+    </row>
+    <row r="19" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="3"/>
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="3"/>
+    </row>
+    <row r="20" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="2"/>
+    </row>
+    <row r="21" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="3"/>
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="7"/>
+      <c r="G21" s="3"/>
+    </row>
+    <row r="22" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="2"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
+      <c r="G22" s="2"/>
+    </row>
+    <row r="23" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="3"/>
+      <c r="B23" s="3"/>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="7"/>
+      <c r="G23" s="3"/>
+    </row>
+    <row r="24" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="2"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="6"/>
+      <c r="G24" s="2"/>
+    </row>
+    <row r="25" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="3"/>
+      <c r="B25" s="3"/>
+      <c r="C25" s="3"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="7"/>
+      <c r="G25" s="3"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -748,10 +1104,9 @@
     <hyperlink ref="E3" r:id="rId2" xr:uid="{B41FAB88-E51F-43D8-B057-ACD206F129FB}"/>
     <hyperlink ref="E4" r:id="rId3" xr:uid="{14B9C1B5-749C-4628-A58D-91E70CDE055B}"/>
     <hyperlink ref="E5" r:id="rId4" xr:uid="{7B793A24-6321-4979-B5CA-05E4D6AC508F}"/>
-    <hyperlink ref="F2" r:id="rId5" xr:uid="{C1B1F1B0-FD9E-4F9F-9667-A8D0FE1D2301}"/>
-    <hyperlink ref="F3" r:id="rId6" xr:uid="{80148996-AA01-4363-8791-6C80DAB9C19E}"/>
-    <hyperlink ref="F4" r:id="rId7" xr:uid="{372160D2-5864-4F82-8F09-843530621722}"/>
-    <hyperlink ref="F5" r:id="rId8" xr:uid="{B0915ADB-C36F-4888-9665-B761F556F9B8}"/>
+    <hyperlink ref="E6" r:id="rId5" xr:uid="{49C2C9A7-BE41-4991-BAF1-1114754E4D52}"/>
+    <hyperlink ref="E7" r:id="rId6" xr:uid="{5570D874-FCDF-4C3C-9661-A9607E3ADEEB}"/>
+    <hyperlink ref="E13" r:id="rId7" xr:uid="{4281A67C-AC78-4A68-A664-CAB0381ADAA6}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -767,7 +1122,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -775,42 +1130,42 @@
     </row>
     <row r="3" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -818,37 +1173,37 @@
     </row>
     <row r="12" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/ĆWICZENIA.xlsx
+++ b/ĆWICZENIA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DYSK GOOGLE\ĆWICZENIA KONSPEKT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9555A37F-7E1E-4D51-B647-088DA76AAF89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{371EA259-3F0E-4A05-9458-DC8B0EA8F845}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="13305" yWindow="0" windowWidth="25200" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -237,9 +237,6 @@
     <t xml:space="preserve">Fingerstyle, Etiuda, </t>
   </si>
   <si>
-    <t xml:space="preserve">ECONOMY PICKING - Two Strings, Two Directions, Shred, </t>
-  </si>
-  <si>
     <t>Pick Slanting, Shred, Picking, Synchronizacja, Lewa Ręka</t>
   </si>
   <si>
@@ -277,6 +274,9 @@
   </si>
   <si>
     <t xml:space="preserve">Ćwiczenie na niezależne granie melodii oraz basu jednocześnie w rytmie lekkiego shuffle. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECONOMY PICKING - Two Strings, Two Directions </t>
   </si>
 </sst>
 </file>
@@ -739,7 +739,7 @@
         <v>7</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>27</v>
@@ -760,7 +760,7 @@
         <v>8</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>28</v>
@@ -781,7 +781,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>29</v>
@@ -802,7 +802,7 @@
         <v>7</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E5" s="7" t="s">
         <v>30</v>
@@ -835,14 +835,14 @@
     </row>
     <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C7" s="3"/>
       <c r="D7" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>41</v>
@@ -863,7 +863,7 @@
         <v>61</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>50</v>
@@ -884,7 +884,7 @@
         <v>61</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>51</v>
@@ -905,7 +905,7 @@
         <v>61</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>52</v>
@@ -926,7 +926,7 @@
         <v>8</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E11" s="7" t="s">
         <v>53</v>
@@ -947,14 +947,14 @@
         <v>61</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>54</v>
       </c>
       <c r="F12" s="6"/>
       <c r="G12" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -968,14 +968,14 @@
         <v>61</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E13" s="7" t="s">
         <v>55</v>
       </c>
       <c r="F13" s="7"/>
       <c r="G13" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -996,7 +996,7 @@
       </c>
       <c r="F14" s="6"/>
       <c r="G14" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">

--- a/ĆWICZENIA.xlsx
+++ b/ĆWICZENIA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DYSK GOOGLE\ĆWICZENIA KONSPEKT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{371EA259-3F0E-4A05-9458-DC8B0EA8F845}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96C64C19-944F-4F13-9732-C387CC4041CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="13305" yWindow="0" windowWidth="25200" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/ĆWICZENIA.xlsx
+++ b/ĆWICZENIA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DYSK GOOGLE\ĆWICZENIA KONSPEKT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7D59735-5BD3-4A97-B4EC-6A251AFF9480}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0C0B9FA-2B55-459A-817B-32BDD3055C82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="13305" yWindow="0" windowWidth="25200" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/ĆWICZENIA.xlsx
+++ b/ĆWICZENIA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DYSK GOOGLE\ĆWICZENIA KONSPEKT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0C0B9FA-2B55-459A-817B-32BDD3055C82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF5F07E4-E1E5-4253-91C2-B7FF9AF65157}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="13305" yWindow="0" windowWidth="25200" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -276,7 +276,7 @@
     <t xml:space="preserve">Ćwiczenie na niezależne granie melodii oraz basu jednocześnie w rytmie lekkiego shuffle. </t>
   </si>
   <si>
-    <t>ECONOMY PICKING - Two Strings, Two Directions</t>
+    <t>ECONOMY PICKING - Two Strings Two Directions</t>
   </si>
 </sst>
 </file>

--- a/ĆWICZENIA.xlsx
+++ b/ĆWICZENIA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DYSK GOOGLE\ĆWICZENIA KONSPEKT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89699834-4A97-415C-A4E0-41DBA4621203}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD708241-77C0-4EA5-9B59-F284789BC990}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13305" yWindow="0" windowWidth="25200" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ćwiczenia" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="109">
   <si>
     <t>NAZWA</t>
   </si>
@@ -277,6 +277,93 @@
   </si>
   <si>
     <t>TRUDNY</t>
+  </si>
+  <si>
+    <t>LEGATO - 4 Scale Patterns on 2 Strings</t>
+  </si>
+  <si>
+    <t>LEGATO - Drills Exercise</t>
+  </si>
+  <si>
+    <t>LEGATO - Fast Scale Run</t>
+  </si>
+  <si>
+    <t>LEGATO - Full Legato Warm Up</t>
+  </si>
+  <si>
+    <t>LEGATO - Legato Speed Bursts Scale Paterns</t>
+  </si>
+  <si>
+    <t>LEGATO - Mistrzowska sekwencja</t>
+  </si>
+  <si>
+    <t>LEGATO - Pijany Pajączek</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1jWImmk8qzAhIccT5CjME6txZMWuPIE14&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1bc2H0esx4aALl1L1QHfpkJgkxl2AhoBz&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1PoBGsJqnt1Q4LuxouSfHT_FpD98-wTBh&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1UelrJQXiih8Vsadk2LBKB7a-huwcdBpi&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1ZlLcLDZ6y1NX0fptFyIHY9h-DNrcbfkM&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1SwJa_Lp4t2OItUnemmonEn_bflWzz-YU&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1TEBiDCiYMuzt_hOWSzFAkLeP0KowdaxI&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>LEGATO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W tym ćwiczeniu ograsz za pomocą legato wszystkie cztery popularne opalcowania, które znajdziesz w każdej skali muzycznej. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ćwiczenie na hammer-ony i pull-offy w oparciu o różne opalcowania skal. Typowa gitarowa wprawka. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Szybka zagrywka legato, dzięki której wyćwiczysz nietypową sekwencję dźwięków. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pełna rozgrzewka legato, zawierająca całą masę ćwiczeń w różnych kombinacjach. </t>
+  </si>
+  <si>
+    <t>Ćwiczenie na synchronizację obu dłoni za pomocą tak zwanego „pajączka” oraz legato.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ćwiczenie na płynne wykonywanie hammeronów w różnych kombinacjach opalsowań, tak zwanych sekwencjach. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ćwiczenie legato w oparciu o tzw. Speed Bursty oraz trzy popularne opalcowania skal muzycznych. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legato, Skale, Sekwencje, Shred, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legato, Skale, Zmiana strun, Shred, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legato, Wprawki, Speed Burst, Shred, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legato, Skale, Speed Burst, Shred, Wprawki, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legato, Skale, Sekwencje, Wprawki, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legato, Pajączki, Sekwencje, Wprawki, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legato, Wprawki, Rozgrzewka, </t>
   </si>
 </sst>
 </file>
@@ -693,7 +780,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G51"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35" customWidth="1"/>
@@ -1002,67 +1089,151 @@
       </c>
     </row>
     <row r="15" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="3"/>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="7"/>
+      <c r="A15" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>87</v>
+      </c>
       <c r="F15" s="7"/>
-      <c r="G15" s="3"/>
+      <c r="G15" s="3" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="16" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="6"/>
+      <c r="A16" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>88</v>
+      </c>
       <c r="F16" s="6"/>
-      <c r="G16" s="2"/>
+      <c r="G16" s="2" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="17" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="3"/>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="7"/>
+      <c r="A17" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>89</v>
+      </c>
       <c r="F17" s="7"/>
-      <c r="G17" s="3"/>
+      <c r="G17" s="3" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="18" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="6"/>
+      <c r="A18" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>90</v>
+      </c>
       <c r="F18" s="6"/>
-      <c r="G18" s="2"/>
+      <c r="G18" s="2" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="19" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="3"/>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="7"/>
+      <c r="A19" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>91</v>
+      </c>
       <c r="F19" s="7"/>
-      <c r="G19" s="3"/>
+      <c r="G19" s="3" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="20" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="6"/>
+      <c r="A20" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>92</v>
+      </c>
       <c r="F20" s="6"/>
-      <c r="G20" s="2"/>
+      <c r="G20" s="2" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="21" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="3"/>
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
-      <c r="E21" s="7"/>
+      <c r="A21" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>93</v>
+      </c>
       <c r="F21" s="7"/>
-      <c r="G21" s="3"/>
+      <c r="G21" s="3" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="22" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2"/>
@@ -1099,6 +1270,240 @@
       <c r="E25" s="7"/>
       <c r="F25" s="7"/>
       <c r="G25" s="3"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="2"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="6"/>
+      <c r="G26" s="2"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="3"/>
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
+      <c r="D27" s="3"/>
+      <c r="E27" s="7"/>
+      <c r="F27" s="7"/>
+      <c r="G27" s="3"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="2"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="6"/>
+      <c r="F28" s="6"/>
+      <c r="G28" s="2"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="3"/>
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
+      <c r="D29" s="3"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="7"/>
+      <c r="G29" s="3"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="2"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="6"/>
+      <c r="F30" s="6"/>
+      <c r="G30" s="2"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="3"/>
+      <c r="B31" s="3"/>
+      <c r="C31" s="3"/>
+      <c r="D31" s="3"/>
+      <c r="E31" s="7"/>
+      <c r="F31" s="7"/>
+      <c r="G31" s="3"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="2"/>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="6"/>
+      <c r="F32" s="6"/>
+      <c r="G32" s="2"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="3"/>
+      <c r="B33" s="3"/>
+      <c r="C33" s="3"/>
+      <c r="D33" s="3"/>
+      <c r="E33" s="7"/>
+      <c r="F33" s="7"/>
+      <c r="G33" s="3"/>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" s="2"/>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="6"/>
+      <c r="F34" s="6"/>
+      <c r="G34" s="2"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" s="3"/>
+      <c r="B35" s="3"/>
+      <c r="C35" s="3"/>
+      <c r="D35" s="3"/>
+      <c r="E35" s="7"/>
+      <c r="F35" s="7"/>
+      <c r="G35" s="3"/>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="2"/>
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="6"/>
+      <c r="F36" s="6"/>
+      <c r="G36" s="2"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" s="3"/>
+      <c r="B37" s="3"/>
+      <c r="C37" s="3"/>
+      <c r="D37" s="3"/>
+      <c r="E37" s="7"/>
+      <c r="F37" s="7"/>
+      <c r="G37" s="3"/>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" s="2"/>
+      <c r="B38" s="2"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="6"/>
+      <c r="G38" s="2"/>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" s="3"/>
+      <c r="B39" s="3"/>
+      <c r="C39" s="3"/>
+      <c r="D39" s="3"/>
+      <c r="E39" s="7"/>
+      <c r="F39" s="7"/>
+      <c r="G39" s="3"/>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" s="2"/>
+      <c r="B40" s="2"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="6"/>
+      <c r="G40" s="2"/>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" s="3"/>
+      <c r="B41" s="3"/>
+      <c r="C41" s="3"/>
+      <c r="D41" s="3"/>
+      <c r="E41" s="7"/>
+      <c r="F41" s="7"/>
+      <c r="G41" s="3"/>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" s="2"/>
+      <c r="B42" s="2"/>
+      <c r="C42" s="2"/>
+      <c r="D42" s="2"/>
+      <c r="E42" s="6"/>
+      <c r="F42" s="6"/>
+      <c r="G42" s="2"/>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" s="3"/>
+      <c r="B43" s="3"/>
+      <c r="C43" s="3"/>
+      <c r="D43" s="3"/>
+      <c r="E43" s="7"/>
+      <c r="F43" s="7"/>
+      <c r="G43" s="3"/>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" s="2"/>
+      <c r="B44" s="2"/>
+      <c r="C44" s="2"/>
+      <c r="D44" s="2"/>
+      <c r="E44" s="6"/>
+      <c r="F44" s="6"/>
+      <c r="G44" s="2"/>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" s="3"/>
+      <c r="B45" s="3"/>
+      <c r="C45" s="3"/>
+      <c r="D45" s="3"/>
+      <c r="E45" s="7"/>
+      <c r="F45" s="7"/>
+      <c r="G45" s="3"/>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" s="2"/>
+      <c r="B46" s="2"/>
+      <c r="C46" s="2"/>
+      <c r="D46" s="2"/>
+      <c r="E46" s="6"/>
+      <c r="F46" s="6"/>
+      <c r="G46" s="2"/>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" s="3"/>
+      <c r="B47" s="3"/>
+      <c r="C47" s="3"/>
+      <c r="D47" s="3"/>
+      <c r="E47" s="7"/>
+      <c r="F47" s="7"/>
+      <c r="G47" s="3"/>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48" s="2"/>
+      <c r="B48" s="2"/>
+      <c r="C48" s="2"/>
+      <c r="D48" s="2"/>
+      <c r="E48" s="6"/>
+      <c r="F48" s="6"/>
+      <c r="G48" s="2"/>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A49" s="3"/>
+      <c r="B49" s="3"/>
+      <c r="C49" s="3"/>
+      <c r="D49" s="3"/>
+      <c r="E49" s="7"/>
+      <c r="F49" s="7"/>
+      <c r="G49" s="3"/>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A50" s="2"/>
+      <c r="B50" s="2"/>
+      <c r="C50" s="2"/>
+      <c r="D50" s="2"/>
+      <c r="E50" s="6"/>
+      <c r="F50" s="6"/>
+      <c r="G50" s="2"/>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A51" s="3"/>
+      <c r="B51" s="3"/>
+      <c r="C51" s="3"/>
+      <c r="D51" s="3"/>
+      <c r="E51" s="7"/>
+      <c r="F51" s="7"/>
+      <c r="G51" s="3"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -1109,9 +1514,11 @@
     <hyperlink ref="E6" r:id="rId5" xr:uid="{49C2C9A7-BE41-4991-BAF1-1114754E4D52}"/>
     <hyperlink ref="E7" r:id="rId6" xr:uid="{5570D874-FCDF-4C3C-9661-A9607E3ADEEB}"/>
     <hyperlink ref="E13" r:id="rId7" xr:uid="{4281A67C-AC78-4A68-A664-CAB0381ADAA6}"/>
+    <hyperlink ref="E17" r:id="rId8" xr:uid="{C020F178-7F0C-4255-84C0-D02096F78587}"/>
+    <hyperlink ref="E19" r:id="rId9" xr:uid="{32919252-880A-47F2-A773-C93662E9BCDB}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId8"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId10"/>
 </worksheet>
 </file>
 

--- a/ĆWICZENIA.xlsx
+++ b/ĆWICZENIA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DYSK GOOGLE\ĆWICZENIA KONSPEKT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD708241-77C0-4EA5-9B59-F284789BC990}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A952A7E-0818-4F00-BF0B-263537D69CF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13305" yWindow="0" windowWidth="25200" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ćwiczenia" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="183">
   <si>
     <t>NAZWA</t>
   </si>
@@ -364,6 +364,229 @@
   </si>
   <si>
     <t xml:space="preserve">Legato, Wprawki, Rozgrzewka, </t>
+  </si>
+  <si>
+    <t>PICKING -  Bursty 16tkowe + Triolowy Finish</t>
+  </si>
+  <si>
+    <t>PICKING - Bursty 16tkowe</t>
+  </si>
+  <si>
+    <t>PICKING - Bursty Triole</t>
+  </si>
+  <si>
+    <t>PICKING - Crazy Picking Bursts</t>
+  </si>
+  <si>
+    <t>PICKING - Picking Bursts Down Stroke First</t>
+  </si>
+  <si>
+    <t>PICKING - Picking Bursts Up Stroke First</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1c-7RQCl688uPo1g-uHi8cV15lDjw71-J&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1nsH-7vyXsyhPwXhfp3eO2i0UoRbj9rZf&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1c31Zg-EqroNdGdt_eyVSDJezVMb4S6dw&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1nSnAaqVHT0lZ03JZ_pphRANsuR4y5wj-&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1nV92CG7TvHuwELgG9NPDTDaeYKyaV1ds&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1ouHRv2uOSif-Bglcxe4d8ib5t1NEsZ0K&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>PICKING</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Picking, </t>
+  </si>
+  <si>
+    <t>RYTM</t>
+  </si>
+  <si>
+    <t>RYTM - 8 LVL Rytmu</t>
+  </si>
+  <si>
+    <t>RYTM - Nauka Wartości Rytmicznych</t>
+  </si>
+  <si>
+    <t>RYTM - Zmiany Wartości Rytmicznych 1#</t>
+  </si>
+  <si>
+    <t>RYTM - Zmiany Wartości Rytmicznych 2#</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1-y1UZbq9gyAqEmokvBmKiGvhFlZdByim&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=0B-ZsE-2yneXreHNlWlN1Qk9QU3c&amp;resourcekey=0-zw_KTiuqgc8666ZnLSEJBQ&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1eSK7sRMW6L73YYsurYsB5zGNhEhgzCAN&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1E568MYZJsyGA1hjokOnIMBASi-4jy90u&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>SHRED</t>
+  </si>
+  <si>
+    <t>SHRED - Burst of String Changes</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1TLA9XaP2CV4UhQKKPjUrmxe_JWG9ubO-&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>SHRED - Harry Shreder I Komnata Dwóch Strun</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1T1zlrq8VgWH1MXTuoKrMk8cba2cCMMLQ&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>SHRED - Pickslanting Ascending Exercise</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1Yk2M7HltnSsRjXZMLm9KRcvxmYeaMszz&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>SHRED - Pickslanting Descending Exercise</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1LvqV7bWhmGjLWpJdf77RiEkZAm-z-yqZ&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>SHRED - Shred Starter 01</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1-4M7HqhQge6ioNb0BgbPM9aAoqJMYNLe&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>SHRED - Shredo-Strada</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1SyWnVmYzR643V9ggK8Z_jE7fUrH83CDT&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>SHRED - Trzej Muszkieterowie Shredu</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1QkJzyIfPMSoudmh4LctcRnxRm3C4OSFI&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>SHRED - Two Strings, One Neck</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1tI8X-z9WWKpwQR7FJJQymdNLOf9sHGFr&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>SHRED - Wyprzedzanie na dwu-pasmówce</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=11hB3wLNob8lfa_cXuwJW2rrssCfV4LMl&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>SHRED - Shredo-Strada Bursty A</t>
+  </si>
+  <si>
+    <t>SHRED - Shredo-Strada Bursty B</t>
+  </si>
+  <si>
+    <t>SHRED - Shredo-Strada Bursty Długie A</t>
+  </si>
+  <si>
+    <t>SHRED - Shredo-Strada Bursty Długie B</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1JIplVpPerd4VXB9kRjFNOCnf_8UkULy7&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1L7ielj6hb2GhSdKL2ufCfUzH2wG8T1PB&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1sBrlkSIZniyeIihRhX2dYICuPCxFTFHn&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1uDF3pG6LuDEM8eWx3CSKJ-lPbyaX4wAj&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rytm, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shred, </t>
+  </si>
+  <si>
+    <t>PROSTY, ŚREDNI, TRUDNY</t>
+  </si>
+  <si>
+    <t>Ćwiczenie na szybkość kostkowania zbudowane w oparciu o szesnastkowe Bursty z triolowym finiszem dającym dodatkowego kopa!</t>
+  </si>
+  <si>
+    <t>Ćwiczenie na szybkość kostkowania zbudowane w oparciu o szesnastkowe Bursty.</t>
+  </si>
+  <si>
+    <t>Ćwiczenie na szybkość kostkowania zbudowane w oparciu o triolowe Bursty.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ćwiczenie na szybkość kostkowania zbudowane w oparciu o rytm szesnastkowy oraz bursty o różnej długości. Wykonasz to ćwiczenie na całym gryfie. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ćwiczenie na szybkość kostkowania za pomocą burstów szesnastkowych o różnej długości. Pierwsze uderzenie: kostkuj w dół. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ćwiczenie na szybkość kostkowania za pomocą burstów szesnastkowych o różnej długości. Pierwsze uderzenie: kostkuj w górę. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sprawdź, na którym poziomie rytmiki jesteś. Jest to ćwiczenie, dzięki któremu opanujesz płynną zmianę praktycznie wszystkich wartości rytmicznych. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ćwiczenie na naukę oraz zmianę wartości rytmicznych. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ćwiczenie na dwóch strunach, dzięki któremu nauczysz się płynnie przechodzić po całej gryfie, ćwicząc wszystkie możliwe opalcowania. Dzięki Speed Burstom na końcu każdej pozycji poćwiczysz prędkość. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Świetne ćwiczenie na shredowe granie i zmianę strun. Pamiętaj, że podwajamy pierwszy oraz ostatni dźwięk. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ćwiczenie na zmianę strun od grubszej do cieńszej za pomocą Pick Slantingu. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ćwiczenie na zmianę strun od cieńszej do grubszej za pomocą Pick Slantingu. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zagrywka, która świetnie nadaje się do nauki szredu, wykonaj ją kostkowaniem naprzemiennym pochylonym w dół. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">To ćwiczenie, dzięki któremu zbudujesz szybkość gry. Jest grane na jednej strunie oraz zawiera "speed burst". Koniecznie graj w pełnym rozluźnieniu, tylko jednym palcem na raz. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ćwiczenie na wszystkie opalcowania skali wzdłuż jednej struny.
+Bursty szesnastkowe z kierunkiem dźwięków do przodu. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ćwiczenie na wszystkie opalcowania skali wzdłuż jednej struny. Bursty szesnastkowe z kierunkiem dźwięków do tyłu. </t>
+  </si>
+  <si>
+    <t>Ćwiczenie na wszystkie opalcowania skali wzdłuż jednej struny. Bursty szesnastkowe z kierunkiem dźwięków do przodu. Wersja przedłużona.</t>
+  </si>
+  <si>
+    <t>Ćwiczenie na wszystkie opalcowania skali wzdłuż jednej struny. Bursty szesnastkowe z kierunkiem dźwięków do tyłu. Wersja przedłużona.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mordercze ćwiczenie, w którym powtarzasz dwa razy tę samą sekwencję na jednej strunie. Lecisz przez wszystkie struny tam i z powrotem, zachowując płaszczyznę kostkowania pochłoniętą w dół. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Szybka etiuda na dwie struny, przechodząca przez cały gryf.  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ćwiczenie, dzięki któremu opanujesz płynną zmianę pozycji na gryfie. Nie ma nawet chwili wytchnienia; zmieniasz pozycję co kilka dźwięków. </t>
   </si>
 </sst>
 </file>
@@ -780,8 +1003,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G51"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:G55"/>
+  <sheetFormatPr defaultRowHeight="35.1" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -792,7 +1015,7 @@
     <col min="7" max="7" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -815,7 +1038,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>23</v>
       </c>
@@ -836,7 +1059,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>29</v>
       </c>
@@ -857,7 +1080,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>30</v>
       </c>
@@ -878,7 +1101,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>31</v>
       </c>
@@ -899,7 +1122,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>36</v>
       </c>
@@ -920,7 +1143,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>76</v>
       </c>
@@ -941,7 +1164,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>41</v>
       </c>
@@ -962,7 +1185,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>42</v>
       </c>
@@ -983,7 +1206,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>43</v>
       </c>
@@ -1004,7 +1227,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>44</v>
       </c>
@@ -1025,7 +1248,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>45</v>
       </c>
@@ -1046,7 +1269,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>46</v>
       </c>
@@ -1067,7 +1290,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>47</v>
       </c>
@@ -1088,7 +1311,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>80</v>
       </c>
@@ -1109,7 +1332,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>81</v>
       </c>
@@ -1130,7 +1353,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>82</v>
       </c>
@@ -1151,7 +1374,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>83</v>
       </c>
@@ -1172,7 +1395,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>84</v>
       </c>
@@ -1193,7 +1416,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>85</v>
       </c>
@@ -1214,7 +1437,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>86</v>
       </c>
@@ -1235,214 +1458,490 @@
         <v>99</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="2"/>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="6"/>
+    <row r="22" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>115</v>
+      </c>
       <c r="F22" s="6"/>
-      <c r="G22" s="2"/>
-    </row>
-    <row r="23" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="3"/>
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
-      <c r="E23" s="7"/>
+      <c r="G22" s="2" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>116</v>
+      </c>
       <c r="F23" s="7"/>
-      <c r="G23" s="3"/>
-    </row>
-    <row r="24" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="2"/>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="6"/>
+      <c r="G23" s="3" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>117</v>
+      </c>
       <c r="F24" s="6"/>
-      <c r="G24" s="2"/>
-    </row>
-    <row r="25" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="3"/>
-      <c r="B25" s="3"/>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
-      <c r="E25" s="7"/>
+      <c r="G24" s="3" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>118</v>
+      </c>
       <c r="F25" s="7"/>
-      <c r="G25" s="3"/>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="2"/>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="6"/>
+      <c r="G25" s="3" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>119</v>
+      </c>
       <c r="F26" s="6"/>
-      <c r="G26" s="2"/>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="3"/>
-      <c r="B27" s="3"/>
-      <c r="C27" s="3"/>
-      <c r="D27" s="3"/>
-      <c r="E27" s="7"/>
+      <c r="G26" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>120</v>
+      </c>
       <c r="F27" s="7"/>
-      <c r="G27" s="3"/>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="2"/>
-      <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="6"/>
+      <c r="G27" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>128</v>
+      </c>
       <c r="F28" s="6"/>
-      <c r="G28" s="2"/>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="3"/>
-      <c r="B29" s="3"/>
-      <c r="C29" s="3"/>
-      <c r="D29" s="3"/>
-      <c r="E29" s="7"/>
+      <c r="G28" s="2" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>129</v>
+      </c>
       <c r="F29" s="7"/>
-      <c r="G29" s="3"/>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="2"/>
-      <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
-      <c r="E30" s="6"/>
+      <c r="G29" s="3" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>130</v>
+      </c>
       <c r="F30" s="6"/>
-      <c r="G30" s="2"/>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="3"/>
-      <c r="B31" s="3"/>
-      <c r="C31" s="3"/>
-      <c r="D31" s="3"/>
-      <c r="E31" s="7"/>
+      <c r="G30" s="2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>131</v>
+      </c>
       <c r="F31" s="7"/>
-      <c r="G31" s="3"/>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="2"/>
-      <c r="B32" s="2"/>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2"/>
-      <c r="E32" s="6"/>
+      <c r="G31" s="3" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>134</v>
+      </c>
       <c r="F32" s="6"/>
-      <c r="G32" s="2"/>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="3"/>
-      <c r="B33" s="3"/>
-      <c r="C33" s="3"/>
-      <c r="D33" s="3"/>
-      <c r="E33" s="7"/>
+      <c r="G32" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>136</v>
+      </c>
       <c r="F33" s="7"/>
-      <c r="G33" s="3"/>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="2"/>
-      <c r="B34" s="2"/>
-      <c r="C34" s="2"/>
-      <c r="D34" s="2"/>
-      <c r="E34" s="6"/>
+      <c r="G33" s="3" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>138</v>
+      </c>
       <c r="F34" s="6"/>
-      <c r="G34" s="2"/>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="3"/>
-      <c r="B35" s="3"/>
-      <c r="C35" s="3"/>
-      <c r="D35" s="3"/>
-      <c r="E35" s="7"/>
+      <c r="G34" s="2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>140</v>
+      </c>
       <c r="F35" s="7"/>
-      <c r="G35" s="3"/>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="2"/>
-      <c r="B36" s="2"/>
-      <c r="C36" s="2"/>
-      <c r="D36" s="2"/>
-      <c r="E36" s="6"/>
+      <c r="G35" s="3" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>142</v>
+      </c>
       <c r="F36" s="6"/>
-      <c r="G36" s="2"/>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="3"/>
-      <c r="B37" s="3"/>
-      <c r="C37" s="3"/>
-      <c r="D37" s="3"/>
-      <c r="E37" s="7"/>
+      <c r="G36" s="2" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>144</v>
+      </c>
       <c r="F37" s="7"/>
-      <c r="G37" s="3"/>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="2"/>
-      <c r="B38" s="2"/>
-      <c r="C38" s="2"/>
-      <c r="D38" s="2"/>
-      <c r="E38" s="6"/>
-      <c r="F38" s="6"/>
-      <c r="G38" s="2"/>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="3"/>
-      <c r="B39" s="3"/>
-      <c r="C39" s="3"/>
-      <c r="D39" s="3"/>
-      <c r="E39" s="7"/>
+      <c r="G37" s="3" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="F38" s="7"/>
+      <c r="G38" s="3" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="E39" s="7" t="s">
+        <v>156</v>
+      </c>
       <c r="F39" s="7"/>
-      <c r="G39" s="3"/>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="2"/>
-      <c r="B40" s="2"/>
-      <c r="C40" s="2"/>
-      <c r="D40" s="2"/>
-      <c r="E40" s="6"/>
-      <c r="F40" s="6"/>
-      <c r="G40" s="2"/>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="3"/>
-      <c r="B41" s="3"/>
-      <c r="C41" s="3"/>
-      <c r="D41" s="3"/>
-      <c r="E41" s="7"/>
+      <c r="G39" s="3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="F40" s="7"/>
+      <c r="G40" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>158</v>
+      </c>
       <c r="F41" s="7"/>
-      <c r="G41" s="3"/>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="2"/>
-      <c r="B42" s="2"/>
-      <c r="C42" s="2"/>
-      <c r="D42" s="2"/>
-      <c r="E42" s="6"/>
+      <c r="G41" s="3" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>146</v>
+      </c>
       <c r="F42" s="6"/>
-      <c r="G42" s="2"/>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="3"/>
-      <c r="B43" s="3"/>
-      <c r="C43" s="3"/>
-      <c r="D43" s="3"/>
-      <c r="E43" s="7"/>
+      <c r="G42" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="E43" s="7" t="s">
+        <v>148</v>
+      </c>
       <c r="F43" s="7"/>
-      <c r="G43" s="3"/>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="2"/>
-      <c r="B44" s="2"/>
-      <c r="C44" s="2"/>
-      <c r="D44" s="2"/>
-      <c r="E44" s="6"/>
+      <c r="G43" s="3" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="E44" s="6" t="s">
+        <v>150</v>
+      </c>
       <c r="F44" s="6"/>
-      <c r="G44" s="2"/>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G44" s="2" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="3"/>
       <c r="B45" s="3"/>
       <c r="C45" s="3"/>
@@ -1451,7 +1950,7 @@
       <c r="F45" s="7"/>
       <c r="G45" s="3"/>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
@@ -1460,7 +1959,7 @@
       <c r="F46" s="6"/>
       <c r="G46" s="2"/>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="3"/>
       <c r="B47" s="3"/>
       <c r="C47" s="3"/>
@@ -1469,7 +1968,7 @@
       <c r="F47" s="7"/>
       <c r="G47" s="3"/>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
@@ -1478,7 +1977,7 @@
       <c r="F48" s="6"/>
       <c r="G48" s="2"/>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="3"/>
       <c r="B49" s="3"/>
       <c r="C49" s="3"/>
@@ -1487,7 +1986,7 @@
       <c r="F49" s="7"/>
       <c r="G49" s="3"/>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
@@ -1496,7 +1995,7 @@
       <c r="F50" s="6"/>
       <c r="G50" s="2"/>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="3"/>
       <c r="B51" s="3"/>
       <c r="C51" s="3"/>
@@ -1504,6 +2003,42 @@
       <c r="E51" s="7"/>
       <c r="F51" s="7"/>
       <c r="G51" s="3"/>
+    </row>
+    <row r="52" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="2"/>
+      <c r="B52" s="2"/>
+      <c r="C52" s="2"/>
+      <c r="D52" s="2"/>
+      <c r="E52" s="6"/>
+      <c r="F52" s="6"/>
+      <c r="G52" s="2"/>
+    </row>
+    <row r="53" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="3"/>
+      <c r="B53" s="3"/>
+      <c r="C53" s="3"/>
+      <c r="D53" s="3"/>
+      <c r="E53" s="7"/>
+      <c r="F53" s="7"/>
+      <c r="G53" s="3"/>
+    </row>
+    <row r="54" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="2"/>
+      <c r="B54" s="2"/>
+      <c r="C54" s="2"/>
+      <c r="D54" s="2"/>
+      <c r="E54" s="6"/>
+      <c r="F54" s="6"/>
+      <c r="G54" s="2"/>
+    </row>
+    <row r="55" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="3"/>
+      <c r="B55" s="3"/>
+      <c r="C55" s="3"/>
+      <c r="D55" s="3"/>
+      <c r="E55" s="7"/>
+      <c r="F55" s="7"/>
+      <c r="G55" s="3"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/ĆWICZENIA.xlsx
+++ b/ĆWICZENIA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DYSK GOOGLE\ĆWICZENIA KONSPEKT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E77887DA-9271-4081-95FA-BC7FEE9068A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A70963A8-5E69-4E04-A913-286FA0A0EAE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ćwiczenia" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="247">
   <si>
     <t>NAZWA</t>
   </si>
@@ -584,6 +584,201 @@
   </si>
   <si>
     <t xml:space="preserve">Ćwiczenie, dzięki któremu opanujesz płynną zmianę pozycji na gryfie. Nie ma nawet chwili wytchnienia; zmieniasz pozycję co kilka dźwięków. </t>
+  </si>
+  <si>
+    <t>SPIDER</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1ZYPlbvt7LT_Z7hwdvGMu8oWL9jqXsC_f&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1s-jnwyHdJS9RMrxxxyG6-nly3-XcPv1F&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>SPIDER - Pajączek 3D B</t>
+  </si>
+  <si>
+    <t>SPIDER - Pajączek 3D A</t>
+  </si>
+  <si>
+    <t>SPIDER - Pajączek Pionowy</t>
+  </si>
+  <si>
+    <t>SPIDER - Pajączek Poziomy</t>
+  </si>
+  <si>
+    <t>SPIDER - Spider Pickslanting Exercise</t>
+  </si>
+  <si>
+    <t>SPIDER - Spider Speed Bursts</t>
+  </si>
+  <si>
+    <t>SPIDER - Spider String Switching Bursts</t>
+  </si>
+  <si>
+    <t>SPIDER - String Switching Spider</t>
+  </si>
+  <si>
+    <t>SPIDER -Spider Finger Combinations</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1P119t3n2xVcYfuZBsyTX3_CumK2M4SmE&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=19zVUdRSFrwPUmg4t7Xry9RobZN0Avo1O&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1Thkhg9PAVLnWkjA3jjrzwIg-WLC_G5Ob&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1NCLTpzMVRKD9lyp6_Gi0FOURW_SxTXnX&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1VhXlToDWZ2FD96o62iXrKAzWw3Gh-xSh&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1Vhgjcq1dnsv_sodAo-CR5rHRmL8Zgrro&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1a9ZZdJlreI20ElUs70EAL7VIQ161PTx5&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>STRENGTH AND STRETCH</t>
+  </si>
+  <si>
+    <t>STRENGTH AND STRETCH - Burning Hands</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=0B-ZsE-2yneXrV0R3aWZVZzB3ZE0&amp;resourcekey=0-SZXxwdzRPvb14a8xC4B2NQ&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>STRING SKIPPING</t>
+  </si>
+  <si>
+    <t>STRING SKIPPING - Descending String Skip Lick</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1T71IJ1hfCA9whVu4lf2MNhEtM_pb9Z1e&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>STRING SKIPPING - Etiuda 01</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1TI7DgMFNoz-2hnI9pQk3HX3eX_39w_B2&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>STRING SKIPPING - Johnem Petrucci</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=0B-ZsE-2yneXrMnJMN083Qk5XbGc&amp;resourcekey=0-_fMWO_r1mfl0xTMkD7dz4g&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>STRING SKIPPING - Penta String Skip</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1TOW49FfppQ-1-zItq3h0ZihzBgzPeDrz&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>STRING SKIPPING - Pentatonic String Skipping</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1bVBbkg6_l3WlreCBIQ5gZMD-E1TMt-Ay&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>STRING SKIPPING - String Jumper</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1TBeb4sy-_zzJJKH_BC3sXe2msc4RYyEC&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>SWEEP</t>
+  </si>
+  <si>
+    <t>SWEEP - Etiuda Sweep Arpegios</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1EA-3RLBgthwSO2VlA5S7jyOeJc2NVtmC&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>SWEEP - Neo Classic Sweep Arpegio</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1e0VL23VF5M-YTHDkYyXaf3jfE_DJpYF8&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>SWEEP - TRIAD ARPEGGIO TYPES - 5 STRINGS</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1QdX18ExQ_MX6buLldJiOBGkZFrWVTZaL&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>SWEEP - TRIAD ARPEGGIO TYPES - 6 STRINGS</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1Sq5HrOGN3tyNk_sTYUoBp-GAoRurPHE0&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>SYNCHRO</t>
+  </si>
+  <si>
+    <t>SYNCHRO - Synchro Miks</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1YeYlGD7e0YuoY0YbNjKruc5XhzNBwj_K&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>TRACKS</t>
+  </si>
+  <si>
+    <t>TRACKS - Anastasia - Slash</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1PUlMOmBgAnj5V5_1bqVZmLjRUuPUnwJz&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>TRACKS - Gdzie ten który powie mi - Bhratanki</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=14pxqMvkkmE25PRdU9Y3Dlo4O4F4qi55Q&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>TRACKS - Gimme Gimme Gimme</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1n-lxw9PVYnGBCb8gVEXzEoOXenuwrfS_&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>TRACKS - Nyan Cat</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1aDa33fZlUvJfyWd4nvjx_d38Gnzakftg&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>TRACKS - Scarified - Paul Gilbert</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1a6iFibb9m_ttZ9sqY62auNSo2a8xkEvj&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>TRACKS - Summer - Vivaldi</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1bZSzuM6U9JLMS4UR-6ek7T4wO_vD3Uyd&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>TRACKS - Technical Difficulties - Paul Gilbert</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1hpgQEbxCXzu2i4XUaM8-fBoGX3dTeM5c&amp;usp=drive_fs</t>
+  </si>
+  <si>
+    <t>WARMUP</t>
+  </si>
+  <si>
+    <t>WARMUP - Roy Ziv Exercise</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1OLTVJWy69Xttg0oIB-2MaDhPww_eAu3A&amp;usp=drive_fs</t>
   </si>
 </sst>
 </file>
@@ -1029,11 +1224,11 @@
   <sheetFormatPr defaultRowHeight="35.1" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35" customWidth="1"/>
-    <col min="2" max="2" width="20" customWidth="1"/>
-    <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="40" customWidth="1"/>
+    <col min="2" max="2" width="15.28515625" customWidth="1"/>
+    <col min="3" max="3" width="7.7109375" customWidth="1"/>
+    <col min="4" max="4" width="19.85546875" customWidth="1"/>
     <col min="5" max="5" width="60" customWidth="1"/>
-    <col min="6" max="6" width="50" customWidth="1"/>
+    <col min="6" max="6" width="54" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -1917,236 +2112,410 @@
       </c>
     </row>
     <row r="45" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="3"/>
-      <c r="B45" s="3"/>
+      <c r="A45" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>182</v>
+      </c>
       <c r="C45" s="3"/>
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
-      <c r="F45" s="9"/>
+      <c r="F45" s="9" t="s">
+        <v>183</v>
+      </c>
     </row>
     <row r="46" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="2"/>
-      <c r="B46" s="2"/>
+      <c r="A46" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>182</v>
+      </c>
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
       <c r="E46" s="2"/>
-      <c r="F46" s="8"/>
+      <c r="F46" s="8" t="s">
+        <v>184</v>
+      </c>
     </row>
     <row r="47" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="3"/>
-      <c r="B47" s="3"/>
+      <c r="A47" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>182</v>
+      </c>
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
       <c r="E47" s="3"/>
-      <c r="F47" s="9"/>
+      <c r="F47" s="9" t="s">
+        <v>194</v>
+      </c>
     </row>
     <row r="48" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="2"/>
-      <c r="B48" s="2"/>
+      <c r="A48" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>182</v>
+      </c>
       <c r="C48" s="2"/>
       <c r="D48" s="2"/>
       <c r="E48" s="2"/>
-      <c r="F48" s="8"/>
+      <c r="F48" s="8" t="s">
+        <v>195</v>
+      </c>
     </row>
     <row r="49" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="3"/>
-      <c r="B49" s="3"/>
+      <c r="A49" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>182</v>
+      </c>
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
       <c r="E49" s="3"/>
-      <c r="F49" s="9"/>
+      <c r="F49" s="9" t="s">
+        <v>196</v>
+      </c>
     </row>
     <row r="50" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="2"/>
-      <c r="B50" s="2"/>
+      <c r="A50" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>182</v>
+      </c>
       <c r="C50" s="2"/>
       <c r="D50" s="2"/>
       <c r="E50" s="2"/>
-      <c r="F50" s="8"/>
+      <c r="F50" s="8" t="s">
+        <v>197</v>
+      </c>
     </row>
     <row r="51" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="3"/>
-      <c r="B51" s="3"/>
+      <c r="A51" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>182</v>
+      </c>
       <c r="C51" s="3"/>
       <c r="D51" s="3"/>
       <c r="E51" s="3"/>
-      <c r="F51" s="9"/>
+      <c r="F51" s="9" t="s">
+        <v>198</v>
+      </c>
     </row>
     <row r="52" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="2"/>
-      <c r="B52" s="2"/>
+      <c r="A52" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>182</v>
+      </c>
       <c r="C52" s="2"/>
       <c r="D52" s="2"/>
       <c r="E52" s="2"/>
-      <c r="F52" s="8"/>
+      <c r="F52" s="8" t="s">
+        <v>199</v>
+      </c>
     </row>
     <row r="53" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="3"/>
-      <c r="B53" s="3"/>
+      <c r="A53" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>182</v>
+      </c>
       <c r="C53" s="3"/>
       <c r="D53" s="3"/>
       <c r="E53" s="3"/>
-      <c r="F53" s="9"/>
+      <c r="F53" s="9" t="s">
+        <v>200</v>
+      </c>
     </row>
     <row r="54" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="2"/>
-      <c r="B54" s="2"/>
+      <c r="A54" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>201</v>
+      </c>
       <c r="C54" s="2"/>
       <c r="D54" s="2"/>
       <c r="E54" s="2"/>
-      <c r="F54" s="8"/>
+      <c r="F54" s="8" t="s">
+        <v>203</v>
+      </c>
     </row>
     <row r="55" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="3"/>
-      <c r="B55" s="3"/>
+      <c r="A55" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>204</v>
+      </c>
       <c r="C55" s="3"/>
       <c r="D55" s="3"/>
       <c r="E55" s="3"/>
-      <c r="F55" s="9"/>
+      <c r="F55" s="9" t="s">
+        <v>206</v>
+      </c>
     </row>
     <row r="56" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="3"/>
-      <c r="B56" s="3"/>
+      <c r="A56" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>204</v>
+      </c>
       <c r="C56" s="3"/>
       <c r="D56" s="3"/>
       <c r="E56" s="3"/>
-      <c r="F56" s="9"/>
+      <c r="F56" s="9" t="s">
+        <v>208</v>
+      </c>
     </row>
     <row r="57" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="2"/>
-      <c r="B57" s="2"/>
+      <c r="A57" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>204</v>
+      </c>
       <c r="C57" s="2"/>
       <c r="D57" s="2"/>
       <c r="E57" s="2"/>
-      <c r="F57" s="8"/>
+      <c r="F57" s="8" t="s">
+        <v>210</v>
+      </c>
     </row>
     <row r="58" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="3"/>
-      <c r="B58" s="3"/>
+      <c r="A58" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>204</v>
+      </c>
       <c r="C58" s="3"/>
       <c r="D58" s="3"/>
       <c r="E58" s="3"/>
-      <c r="F58" s="9"/>
+      <c r="F58" s="9" t="s">
+        <v>212</v>
+      </c>
     </row>
     <row r="59" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="2"/>
-      <c r="B59" s="2"/>
+      <c r="A59" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>204</v>
+      </c>
       <c r="C59" s="2"/>
       <c r="D59" s="2"/>
       <c r="E59" s="2"/>
-      <c r="F59" s="8"/>
+      <c r="F59" s="8" t="s">
+        <v>214</v>
+      </c>
     </row>
     <row r="60" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="3"/>
-      <c r="B60" s="3"/>
+      <c r="A60" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>204</v>
+      </c>
       <c r="C60" s="3"/>
       <c r="D60" s="3"/>
       <c r="E60" s="3"/>
-      <c r="F60" s="9"/>
+      <c r="F60" s="9" t="s">
+        <v>216</v>
+      </c>
     </row>
     <row r="61" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="2"/>
-      <c r="B61" s="2"/>
+      <c r="A61" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>217</v>
+      </c>
       <c r="C61" s="2"/>
       <c r="D61" s="2"/>
       <c r="E61" s="2"/>
-      <c r="F61" s="8"/>
+      <c r="F61" s="8" t="s">
+        <v>219</v>
+      </c>
     </row>
     <row r="62" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="3"/>
-      <c r="B62" s="3"/>
+      <c r="A62" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>217</v>
+      </c>
       <c r="C62" s="3"/>
       <c r="D62" s="3"/>
       <c r="E62" s="3"/>
-      <c r="F62" s="9"/>
+      <c r="F62" s="9" t="s">
+        <v>221</v>
+      </c>
     </row>
     <row r="63" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="2"/>
-      <c r="B63" s="2"/>
+      <c r="A63" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>217</v>
+      </c>
       <c r="C63" s="2"/>
       <c r="D63" s="2"/>
       <c r="E63" s="2"/>
-      <c r="F63" s="8"/>
+      <c r="F63" s="8" t="s">
+        <v>223</v>
+      </c>
     </row>
     <row r="64" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="3"/>
-      <c r="B64" s="3"/>
+      <c r="A64" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>217</v>
+      </c>
       <c r="C64" s="3"/>
       <c r="D64" s="3"/>
       <c r="E64" s="3"/>
-      <c r="F64" s="9"/>
+      <c r="F64" s="9" t="s">
+        <v>225</v>
+      </c>
     </row>
     <row r="65" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="2"/>
-      <c r="B65" s="2"/>
+      <c r="A65" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>226</v>
+      </c>
       <c r="C65" s="2"/>
       <c r="D65" s="2"/>
       <c r="E65" s="2"/>
-      <c r="F65" s="8"/>
+      <c r="F65" s="8" t="s">
+        <v>228</v>
+      </c>
     </row>
     <row r="66" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="3"/>
-      <c r="B66" s="3"/>
+      <c r="A66" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>229</v>
+      </c>
       <c r="C66" s="3"/>
       <c r="D66" s="3"/>
       <c r="E66" s="3"/>
-      <c r="F66" s="9"/>
+      <c r="F66" s="9" t="s">
+        <v>231</v>
+      </c>
     </row>
     <row r="67" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="2"/>
-      <c r="B67" s="2"/>
+      <c r="A67" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>229</v>
+      </c>
       <c r="C67" s="2"/>
       <c r="D67" s="2"/>
       <c r="E67" s="2"/>
-      <c r="F67" s="8"/>
+      <c r="F67" s="6" t="s">
+        <v>233</v>
+      </c>
     </row>
     <row r="68" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="3"/>
-      <c r="B68" s="3"/>
+      <c r="A68" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>229</v>
+      </c>
       <c r="C68" s="3"/>
       <c r="D68" s="3"/>
       <c r="E68" s="3"/>
-      <c r="F68" s="9"/>
+      <c r="F68" s="9" t="s">
+        <v>235</v>
+      </c>
     </row>
     <row r="69" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="2"/>
-      <c r="B69" s="2"/>
+      <c r="A69" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>229</v>
+      </c>
       <c r="C69" s="2"/>
       <c r="D69" s="2"/>
       <c r="E69" s="2"/>
-      <c r="F69" s="8"/>
+      <c r="F69" s="8" t="s">
+        <v>237</v>
+      </c>
     </row>
     <row r="70" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="3"/>
-      <c r="B70" s="3"/>
+      <c r="A70" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>229</v>
+      </c>
       <c r="C70" s="3"/>
       <c r="D70" s="3"/>
       <c r="E70" s="3"/>
-      <c r="F70" s="9"/>
+      <c r="F70" s="9" t="s">
+        <v>239</v>
+      </c>
     </row>
     <row r="71" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="2"/>
-      <c r="B71" s="2"/>
+      <c r="A71" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>229</v>
+      </c>
       <c r="C71" s="2"/>
       <c r="D71" s="2"/>
       <c r="E71" s="2"/>
-      <c r="F71" s="8"/>
+      <c r="F71" s="8" t="s">
+        <v>241</v>
+      </c>
     </row>
     <row r="72" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="3"/>
-      <c r="B72" s="3"/>
+      <c r="A72" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>229</v>
+      </c>
       <c r="C72" s="3"/>
       <c r="D72" s="3"/>
       <c r="E72" s="3"/>
-      <c r="F72" s="9"/>
+      <c r="F72" s="9" t="s">
+        <v>243</v>
+      </c>
     </row>
     <row r="73" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="2"/>
-      <c r="B73" s="2"/>
+      <c r="A73" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>244</v>
+      </c>
       <c r="C73" s="2"/>
       <c r="D73" s="2"/>
       <c r="E73" s="2"/>
-      <c r="F73" s="8"/>
+      <c r="F73" s="8" t="s">
+        <v>246</v>
+      </c>
     </row>
     <row r="74" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="3"/>
@@ -2255,9 +2624,10 @@
     <hyperlink ref="F13" r:id="rId7" xr:uid="{4281A67C-AC78-4A68-A664-CAB0381ADAA6}"/>
     <hyperlink ref="F17" r:id="rId8" xr:uid="{C020F178-7F0C-4255-84C0-D02096F78587}"/>
     <hyperlink ref="F19" r:id="rId9" xr:uid="{32919252-880A-47F2-A773-C93662E9BCDB}"/>
+    <hyperlink ref="F67" r:id="rId10" xr:uid="{D2B6880C-A11D-476C-9E19-250564686AE4}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId10"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId11"/>
 </worksheet>
 </file>
 

--- a/ĆWICZENIA.xlsx
+++ b/ĆWICZENIA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DYSK GOOGLE\ĆWICZENIA KONSPEKT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A70963A8-5E69-4E04-A913-286FA0A0EAE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A884CCC-DF99-44E8-B5B1-9687000F55B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
